--- a/podaci/Termini Leto 2026.xlsx
+++ b/podaci/Termini Leto 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\FK_Baranda_sajt\podaci\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF59C6C-6C65-43D9-84FC-F077EB91CCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1647DD7B-69AC-4EE1-B594-BFD47991538C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fudbal Bezanija Termini" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="58">
   <si>
     <t>No.</t>
   </si>
@@ -988,47 +988,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI371"/>
-  <sheetFormatPr defaultColWidth="7.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8" style="38" customWidth="1"/>
-    <col min="18" max="18" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.33203125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="7.44140625" style="1"/>
+    <col min="28" max="28" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="7.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="2" customFormat="1" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" s="2" customFormat="1" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>1</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <v>1</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>1</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="25">
         <v>1</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>1</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>2</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>2</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>2</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>2</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>2</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>2</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>2</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>2</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>2</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>2</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>2</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>2</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>3</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>3</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="18">
         <v>3</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="18">
         <v>3</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="18">
         <v>3</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="18">
         <v>3</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="18">
         <v>3</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="18">
         <v>3</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="18">
         <v>3</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
         <v>3</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
         <v>3</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
         <v>3</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="18">
         <v>4</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" s="18">
         <v>4</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="18">
         <v>4</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="18">
         <v>4</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
         <v>4</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="18">
         <v>4</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="18">
         <v>4</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" s="18">
         <v>4</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" s="18">
         <v>4</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="18">
         <v>4</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="18">
         <v>4</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="18">
         <v>4</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="18">
         <v>5</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="18">
         <v>5</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="18">
         <v>5</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="18">
         <v>5</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="18">
         <v>5</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="18">
         <v>5</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="18">
         <v>5</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
         <v>5</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
         <v>5</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="18">
         <v>5</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="18">
         <v>5</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" s="18">
         <v>5</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="18">
         <v>6</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="18">
         <v>6</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="18">
         <v>6</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="18">
         <v>6</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="18">
         <v>6</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65" s="18">
         <v>6</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" s="18">
         <v>6</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67" s="18">
         <v>6</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68" s="18">
         <v>6</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69" s="18">
         <v>6</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70" s="18">
         <v>6</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71" s="18">
         <v>6</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72" s="18">
         <v>7</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" s="18">
         <v>7</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74" s="18">
         <v>7</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75" s="18">
         <v>7</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" s="18">
         <v>7</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="18">
         <v>7</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78" s="18">
         <v>7</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" s="18">
         <v>7</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" s="18">
         <v>7</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" s="18">
         <v>7</v>
       </c>
@@ -7135,24 +7135,42 @@
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A82" s="18"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A82" s="18">
+        <v>8</v>
+      </c>
+      <c r="B82" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E82" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+      <c r="F82" s="3">
+        <v>1</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
       <c r="J82" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K82" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K82" s="3">
+        <v>5</v>
+      </c>
       <c r="L82" s="3"/>
       <c r="M82" s="4"/>
       <c r="N82" s="7"/>
@@ -7169,33 +7187,65 @@
       <c r="Y82" s="4"/>
       <c r="Z82" s="5"/>
       <c r="AA82" s="4"/>
-      <c r="AB82" s="5"/>
+      <c r="AB82" s="5">
+        <v>0</v>
+      </c>
       <c r="AC82" s="3"/>
-      <c r="AD82" s="3"/>
-      <c r="AE82" s="3"/>
-      <c r="AF82" s="31"/>
-      <c r="AG82" s="32"/>
-      <c r="AH82" s="32"/>
-      <c r="AI82" s="6"/>
-    </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A83" s="18"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
+      <c r="AD82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI82" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A83" s="18">
+        <v>8</v>
+      </c>
+      <c r="B83" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E83" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="F83" s="3">
+        <v>2</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
       <c r="J83" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
       <c r="L83" s="3"/>
       <c r="M83" s="4"/>
       <c r="N83" s="7"/>
@@ -7212,33 +7262,65 @@
       <c r="Y83" s="4"/>
       <c r="Z83" s="5"/>
       <c r="AA83" s="4"/>
-      <c r="AB83" s="5"/>
+      <c r="AB83" s="5">
+        <v>2</v>
+      </c>
       <c r="AC83" s="3"/>
-      <c r="AD83" s="3"/>
-      <c r="AE83" s="3"/>
-      <c r="AF83" s="31"/>
-      <c r="AG83" s="32"/>
-      <c r="AH83" s="32"/>
-      <c r="AI83" s="6"/>
-    </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A84" s="18"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI83" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A84" s="18">
+        <v>8</v>
+      </c>
+      <c r="B84" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="E84" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3">
+        <v>0</v>
+      </c>
       <c r="J84" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
+      <c r="K84" s="3">
+        <v>7</v>
+      </c>
       <c r="L84" s="3"/>
       <c r="M84" s="4"/>
       <c r="N84" s="7"/>
@@ -7255,33 +7337,65 @@
       <c r="Y84" s="4"/>
       <c r="Z84" s="5"/>
       <c r="AA84" s="4"/>
-      <c r="AB84" s="5"/>
+      <c r="AB84" s="5">
+        <v>2</v>
+      </c>
       <c r="AC84" s="3"/>
-      <c r="AD84" s="3"/>
-      <c r="AE84" s="3"/>
-      <c r="AF84" s="31"/>
-      <c r="AG84" s="32"/>
-      <c r="AH84" s="32"/>
-      <c r="AI84" s="6"/>
-    </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A85" s="18"/>
-      <c r="B85" s="28"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI84" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A85" s="18">
+        <v>8</v>
+      </c>
+      <c r="B85" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="E85" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="F85" s="3">
+        <v>2</v>
+      </c>
+      <c r="G85" s="3">
+        <v>8</v>
+      </c>
+      <c r="H85" s="3">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
       <c r="J85" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
       <c r="L85" s="3"/>
       <c r="M85" s="4"/>
       <c r="N85" s="7"/>
@@ -7298,33 +7412,65 @@
       <c r="Y85" s="4"/>
       <c r="Z85" s="5"/>
       <c r="AA85" s="4"/>
-      <c r="AB85" s="5"/>
+      <c r="AB85" s="5">
+        <v>6</v>
+      </c>
       <c r="AC85" s="3"/>
-      <c r="AD85" s="3"/>
-      <c r="AE85" s="3"/>
-      <c r="AF85" s="31"/>
-      <c r="AG85" s="32"/>
-      <c r="AH85" s="32"/>
-      <c r="AI85" s="6"/>
-    </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A86" s="18"/>
-      <c r="B86" s="28"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI85" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A86" s="18">
+        <v>8</v>
+      </c>
+      <c r="B86" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E86" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1</v>
+      </c>
+      <c r="H86" s="3">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
       <c r="J86" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K86" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="K86" s="3">
+        <v>1</v>
+      </c>
       <c r="L86" s="3"/>
       <c r="M86" s="4"/>
       <c r="N86" s="7"/>
@@ -7341,33 +7487,65 @@
       <c r="Y86" s="4"/>
       <c r="Z86" s="5"/>
       <c r="AA86" s="4"/>
-      <c r="AB86" s="5"/>
+      <c r="AB86" s="5">
+        <v>1</v>
+      </c>
       <c r="AC86" s="3"/>
-      <c r="AD86" s="3"/>
-      <c r="AE86" s="3"/>
-      <c r="AF86" s="31"/>
-      <c r="AG86" s="32"/>
-      <c r="AH86" s="32"/>
-      <c r="AI86" s="6"/>
-    </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A87" s="18"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI86" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A87" s="18">
+        <v>8</v>
+      </c>
+      <c r="B87" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="E87" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1</v>
+      </c>
+      <c r="H87" s="3">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
       <c r="J87" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K87" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="K87" s="3">
+        <v>1</v>
+      </c>
       <c r="L87" s="3"/>
       <c r="M87" s="4"/>
       <c r="N87" s="7"/>
@@ -7384,33 +7562,65 @@
       <c r="Y87" s="4"/>
       <c r="Z87" s="5"/>
       <c r="AA87" s="4"/>
-      <c r="AB87" s="5"/>
+      <c r="AB87" s="5">
+        <v>2</v>
+      </c>
       <c r="AC87" s="3"/>
-      <c r="AD87" s="3"/>
-      <c r="AE87" s="3"/>
-      <c r="AF87" s="31"/>
-      <c r="AG87" s="32"/>
-      <c r="AH87" s="32"/>
-      <c r="AI87" s="6"/>
-    </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A88" s="18"/>
-      <c r="B88" s="28"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI87" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A88" s="18">
+        <v>8</v>
+      </c>
+      <c r="B88" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="E88" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <v>5</v>
+      </c>
+      <c r="H88" s="3">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
       <c r="J88" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K88" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="K88" s="3">
+        <v>1</v>
+      </c>
       <c r="L88" s="3"/>
       <c r="M88" s="4"/>
       <c r="N88" s="7"/>
@@ -7427,33 +7637,65 @@
       <c r="Y88" s="4"/>
       <c r="Z88" s="5"/>
       <c r="AA88" s="4"/>
-      <c r="AB88" s="5"/>
+      <c r="AB88" s="5">
+        <v>3</v>
+      </c>
       <c r="AC88" s="3"/>
-      <c r="AD88" s="3"/>
-      <c r="AE88" s="3"/>
-      <c r="AF88" s="31"/>
-      <c r="AG88" s="32"/>
-      <c r="AH88" s="32"/>
-      <c r="AI88" s="6"/>
-    </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A89" s="18"/>
-      <c r="B89" s="28"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI88" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A89" s="18">
+        <v>8</v>
+      </c>
+      <c r="B89" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="E89" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
       <c r="J89" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K89" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="K89" s="3">
+        <v>1</v>
+      </c>
       <c r="L89" s="3"/>
       <c r="M89" s="4"/>
       <c r="N89" s="7"/>
@@ -7470,33 +7712,65 @@
       <c r="Y89" s="4"/>
       <c r="Z89" s="5"/>
       <c r="AA89" s="4"/>
-      <c r="AB89" s="5"/>
+      <c r="AB89" s="5">
+        <v>5</v>
+      </c>
       <c r="AC89" s="3"/>
-      <c r="AD89" s="3"/>
-      <c r="AE89" s="3"/>
-      <c r="AF89" s="31"/>
-      <c r="AG89" s="32"/>
-      <c r="AH89" s="32"/>
-      <c r="AI89" s="6"/>
-    </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A90" s="18"/>
-      <c r="B90" s="28"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI89" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A90" s="18">
+        <v>8</v>
+      </c>
+      <c r="B90" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="E90" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="3">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
       <c r="J90" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K90" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K90" s="3">
+        <v>2</v>
+      </c>
       <c r="L90" s="3"/>
       <c r="M90" s="4"/>
       <c r="N90" s="7"/>
@@ -7513,33 +7787,65 @@
       <c r="Y90" s="4"/>
       <c r="Z90" s="5"/>
       <c r="AA90" s="4"/>
-      <c r="AB90" s="5"/>
+      <c r="AB90" s="5">
+        <v>3</v>
+      </c>
       <c r="AC90" s="3"/>
-      <c r="AD90" s="3"/>
-      <c r="AE90" s="3"/>
-      <c r="AF90" s="31"/>
-      <c r="AG90" s="32"/>
-      <c r="AH90" s="32"/>
-      <c r="AI90" s="6"/>
-    </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A91" s="18"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
+      <c r="AD90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A91" s="18">
+        <v>8</v>
+      </c>
+      <c r="B91" s="28">
+        <v>20260831</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="E91" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
       <c r="J91" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="K91" s="3">
+        <v>5</v>
+      </c>
       <c r="L91" s="3"/>
       <c r="M91" s="4"/>
       <c r="N91" s="7"/>
@@ -7556,16 +7862,30 @@
       <c r="Y91" s="4"/>
       <c r="Z91" s="5"/>
       <c r="AA91" s="4"/>
-      <c r="AB91" s="5"/>
+      <c r="AB91" s="5">
+        <v>2</v>
+      </c>
       <c r="AC91" s="3"/>
-      <c r="AD91" s="3"/>
-      <c r="AE91" s="3"/>
-      <c r="AF91" s="31"/>
-      <c r="AG91" s="32"/>
-      <c r="AH91" s="32"/>
-      <c r="AI91" s="6"/>
-    </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI91" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
       <c r="B92" s="28"/>
       <c r="C92" s="3"/>
@@ -7608,7 +7928,7 @@
       <c r="AH92" s="32"/>
       <c r="AI92" s="6"/>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
       <c r="B93" s="28"/>
       <c r="C93" s="3"/>
@@ -7651,7 +7971,7 @@
       <c r="AH93" s="32"/>
       <c r="AI93" s="6"/>
     </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
       <c r="B94" s="28"/>
       <c r="C94" s="3"/>
@@ -7694,7 +8014,7 @@
       <c r="AH94" s="32"/>
       <c r="AI94" s="6"/>
     </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
       <c r="B95" s="28"/>
       <c r="C95" s="3"/>
@@ -7737,7 +8057,7 @@
       <c r="AH95" s="32"/>
       <c r="AI95" s="6"/>
     </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
       <c r="B96" s="28"/>
       <c r="C96" s="3"/>
@@ -7780,7 +8100,7 @@
       <c r="AH96" s="32"/>
       <c r="AI96" s="6"/>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
       <c r="B97" s="28"/>
       <c r="C97" s="3"/>
@@ -7823,7 +8143,7 @@
       <c r="AH97" s="32"/>
       <c r="AI97" s="6"/>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
       <c r="B98" s="28"/>
       <c r="C98" s="3"/>
@@ -7866,7 +8186,7 @@
       <c r="AH98" s="32"/>
       <c r="AI98" s="6"/>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
       <c r="B99" s="28"/>
       <c r="C99" s="3"/>
@@ -7909,7 +8229,7 @@
       <c r="AH99" s="32"/>
       <c r="AI99" s="6"/>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
       <c r="B100" s="28"/>
       <c r="C100" s="3"/>
@@ -7952,7 +8272,7 @@
       <c r="AH100" s="32"/>
       <c r="AI100" s="6"/>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
       <c r="B101" s="28"/>
       <c r="C101" s="3"/>
@@ -7995,7 +8315,7 @@
       <c r="AH101" s="32"/>
       <c r="AI101" s="6"/>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
       <c r="B102" s="28"/>
       <c r="C102" s="3"/>
@@ -8038,7 +8358,7 @@
       <c r="AH102" s="32"/>
       <c r="AI102" s="6"/>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
       <c r="B103" s="28"/>
       <c r="C103" s="3"/>
@@ -8081,7 +8401,7 @@
       <c r="AH103" s="32"/>
       <c r="AI103" s="6"/>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
       <c r="B104" s="28"/>
       <c r="C104" s="3"/>
@@ -8124,7 +8444,7 @@
       <c r="AH104" s="32"/>
       <c r="AI104" s="6"/>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
       <c r="B105" s="28"/>
       <c r="C105" s="3"/>
@@ -8167,7 +8487,7 @@
       <c r="AH105" s="32"/>
       <c r="AI105" s="6"/>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106" s="18"/>
       <c r="B106" s="28"/>
       <c r="C106" s="3"/>
@@ -8210,7 +8530,7 @@
       <c r="AH106" s="32"/>
       <c r="AI106" s="6"/>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107" s="18"/>
       <c r="B107" s="28"/>
       <c r="C107" s="3"/>
@@ -8253,7 +8573,7 @@
       <c r="AH107" s="32"/>
       <c r="AI107" s="6"/>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108" s="18"/>
       <c r="B108" s="28"/>
       <c r="C108" s="3"/>
@@ -8296,7 +8616,7 @@
       <c r="AH108" s="32"/>
       <c r="AI108" s="6"/>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109" s="18"/>
       <c r="B109" s="28"/>
       <c r="C109" s="3"/>
@@ -8339,7 +8659,7 @@
       <c r="AH109" s="32"/>
       <c r="AI109" s="6"/>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
       <c r="B110" s="28"/>
       <c r="C110" s="3"/>
@@ -8382,7 +8702,7 @@
       <c r="AH110" s="32"/>
       <c r="AI110" s="6"/>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111" s="18"/>
       <c r="B111" s="28"/>
       <c r="C111" s="3"/>
@@ -8425,7 +8745,7 @@
       <c r="AH111" s="32"/>
       <c r="AI111" s="6"/>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112" s="18"/>
       <c r="B112" s="28"/>
       <c r="C112" s="3"/>
@@ -8468,7 +8788,7 @@
       <c r="AH112" s="32"/>
       <c r="AI112" s="6"/>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113" s="18"/>
       <c r="B113" s="28"/>
       <c r="C113" s="3"/>
@@ -8511,7 +8831,7 @@
       <c r="AH113" s="32"/>
       <c r="AI113" s="6"/>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114" s="18"/>
       <c r="B114" s="28"/>
       <c r="C114" s="3"/>
@@ -8554,7 +8874,7 @@
       <c r="AH114" s="32"/>
       <c r="AI114" s="6"/>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115" s="18"/>
       <c r="B115" s="28"/>
       <c r="C115" s="3"/>
@@ -8597,7 +8917,7 @@
       <c r="AH115" s="32"/>
       <c r="AI115" s="6"/>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116" s="18"/>
       <c r="B116" s="28"/>
       <c r="C116" s="3"/>
@@ -8640,7 +8960,7 @@
       <c r="AH116" s="32"/>
       <c r="AI116" s="6"/>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117" s="18"/>
       <c r="B117" s="28"/>
       <c r="C117" s="3"/>
@@ -8683,7 +9003,7 @@
       <c r="AH117" s="32"/>
       <c r="AI117" s="6"/>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118" s="18"/>
       <c r="B118" s="28"/>
       <c r="C118" s="3"/>
@@ -8726,7 +9046,7 @@
       <c r="AH118" s="32"/>
       <c r="AI118" s="6"/>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119" s="18"/>
       <c r="B119" s="28"/>
       <c r="C119" s="3"/>
@@ -8769,7 +9089,7 @@
       <c r="AH119" s="32"/>
       <c r="AI119" s="6"/>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120" s="18"/>
       <c r="B120" s="28"/>
       <c r="C120" s="3"/>
@@ -8812,7 +9132,7 @@
       <c r="AH120" s="32"/>
       <c r="AI120" s="6"/>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121" s="18"/>
       <c r="B121" s="28"/>
       <c r="C121" s="3"/>
@@ -8855,7 +9175,7 @@
       <c r="AH121" s="32"/>
       <c r="AI121" s="6"/>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
       <c r="B122" s="28"/>
       <c r="C122" s="3"/>
@@ -8898,7 +9218,7 @@
       <c r="AH122" s="32"/>
       <c r="AI122" s="6"/>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123" s="18"/>
       <c r="B123" s="28"/>
       <c r="C123" s="3"/>
@@ -8941,7 +9261,7 @@
       <c r="AH123" s="32"/>
       <c r="AI123" s="6"/>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124" s="18"/>
       <c r="B124" s="28"/>
       <c r="C124" s="3"/>
@@ -8984,7 +9304,7 @@
       <c r="AH124" s="32"/>
       <c r="AI124" s="6"/>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125" s="18"/>
       <c r="B125" s="28"/>
       <c r="C125" s="3"/>
@@ -9027,7 +9347,7 @@
       <c r="AH125" s="32"/>
       <c r="AI125" s="6"/>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126" s="18"/>
       <c r="B126" s="28"/>
       <c r="C126" s="3"/>
@@ -9070,7 +9390,7 @@
       <c r="AH126" s="32"/>
       <c r="AI126" s="6"/>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127" s="18"/>
       <c r="B127" s="28"/>
       <c r="C127" s="3"/>
@@ -9113,7 +9433,7 @@
       <c r="AH127" s="32"/>
       <c r="AI127" s="6"/>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128" s="18"/>
       <c r="B128" s="28"/>
       <c r="C128" s="3"/>
@@ -9156,7 +9476,7 @@
       <c r="AH128" s="32"/>
       <c r="AI128" s="6"/>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129" s="18"/>
       <c r="B129" s="28"/>
       <c r="C129" s="3"/>
@@ -9199,7 +9519,7 @@
       <c r="AH129" s="32"/>
       <c r="AI129" s="6"/>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130" s="18"/>
       <c r="B130" s="28"/>
       <c r="C130" s="3"/>
@@ -9242,7 +9562,7 @@
       <c r="AH130" s="32"/>
       <c r="AI130" s="6"/>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131" s="18"/>
       <c r="B131" s="28"/>
       <c r="C131" s="3"/>
@@ -9285,7 +9605,7 @@
       <c r="AH131" s="32"/>
       <c r="AI131" s="6"/>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132" s="18"/>
       <c r="B132" s="28"/>
       <c r="C132" s="3"/>
@@ -9328,7 +9648,7 @@
       <c r="AH132" s="32"/>
       <c r="AI132" s="6"/>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133" s="18"/>
       <c r="B133" s="28"/>
       <c r="C133" s="3"/>
@@ -9371,7 +9691,7 @@
       <c r="AH133" s="32"/>
       <c r="AI133" s="6"/>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
       <c r="B134" s="28"/>
       <c r="C134" s="3"/>
@@ -9413,7 +9733,7 @@
       <c r="AH134" s="32"/>
       <c r="AI134" s="6"/>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135" s="18"/>
       <c r="B135" s="28"/>
       <c r="C135" s="3"/>
@@ -9456,7 +9776,7 @@
       <c r="AH135" s="32"/>
       <c r="AI135" s="6"/>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136" s="18"/>
       <c r="B136" s="28"/>
       <c r="C136" s="3"/>
@@ -9499,7 +9819,7 @@
       <c r="AH136" s="32"/>
       <c r="AI136" s="6"/>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137" s="18"/>
       <c r="B137" s="28"/>
       <c r="C137" s="3"/>
@@ -9542,7 +9862,7 @@
       <c r="AH137" s="32"/>
       <c r="AI137" s="6"/>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138" s="18"/>
       <c r="B138" s="28"/>
       <c r="C138" s="3"/>
@@ -9585,7 +9905,7 @@
       <c r="AH138" s="32"/>
       <c r="AI138" s="6"/>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139" s="18"/>
       <c r="B139" s="28"/>
       <c r="C139" s="3"/>
@@ -9628,7 +9948,7 @@
       <c r="AH139" s="32"/>
       <c r="AI139" s="6"/>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140" s="18"/>
       <c r="B140" s="28"/>
       <c r="C140" s="3"/>
@@ -9671,7 +9991,7 @@
       <c r="AH140" s="32"/>
       <c r="AI140" s="6"/>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141" s="18"/>
       <c r="B141" s="28"/>
       <c r="C141" s="3"/>
@@ -9713,7 +10033,7 @@
       <c r="AH141" s="32"/>
       <c r="AI141" s="6"/>
     </row>
-    <row r="142" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142" s="18"/>
       <c r="B142" s="28"/>
       <c r="C142" s="3"/>
@@ -9756,7 +10076,7 @@
       <c r="AH142" s="32"/>
       <c r="AI142" s="6"/>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143" s="18"/>
       <c r="B143" s="28"/>
       <c r="C143" s="3"/>
@@ -9799,7 +10119,7 @@
       <c r="AH143" s="32"/>
       <c r="AI143" s="6"/>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144" s="18"/>
       <c r="B144" s="28"/>
       <c r="C144" s="3"/>
@@ -9842,7 +10162,7 @@
       <c r="AH144" s="32"/>
       <c r="AI144" s="6"/>
     </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145" s="18"/>
       <c r="B145" s="28"/>
       <c r="C145" s="3"/>
@@ -9885,7 +10205,7 @@
       <c r="AH145" s="32"/>
       <c r="AI145" s="6"/>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146" s="18"/>
       <c r="B146" s="28"/>
       <c r="C146" s="3"/>
@@ -9928,7 +10248,7 @@
       <c r="AH146" s="32"/>
       <c r="AI146" s="6"/>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147" s="18"/>
       <c r="B147" s="28"/>
       <c r="C147" s="3"/>
@@ -9971,7 +10291,7 @@
       <c r="AH147" s="32"/>
       <c r="AI147" s="6"/>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148" s="18"/>
       <c r="B148" s="28"/>
       <c r="C148" s="3"/>
@@ -10014,7 +10334,7 @@
       <c r="AH148" s="32"/>
       <c r="AI148" s="6"/>
     </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149" s="25"/>
       <c r="B149" s="27"/>
       <c r="C149" s="8"/>
@@ -10057,7 +10377,7 @@
       <c r="AH149" s="31"/>
       <c r="AI149" s="12"/>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150" s="25"/>
       <c r="B150" s="27"/>
       <c r="C150" s="8"/>
@@ -10100,7 +10420,7 @@
       <c r="AH150" s="31"/>
       <c r="AI150" s="12"/>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151" s="25"/>
       <c r="B151" s="27"/>
       <c r="C151" s="8"/>
@@ -10143,7 +10463,7 @@
       <c r="AH151" s="31"/>
       <c r="AI151" s="12"/>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152" s="25"/>
       <c r="B152" s="27"/>
       <c r="C152" s="8"/>
@@ -10186,7 +10506,7 @@
       <c r="AH152" s="31"/>
       <c r="AI152" s="12"/>
     </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153" s="25"/>
       <c r="B153" s="27"/>
       <c r="C153" s="8"/>
@@ -10229,7 +10549,7 @@
       <c r="AH153" s="31"/>
       <c r="AI153" s="12"/>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154" s="25"/>
       <c r="B154" s="27"/>
       <c r="C154" s="3"/>
@@ -10272,7 +10592,7 @@
       <c r="AH154" s="31"/>
       <c r="AI154" s="12"/>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155" s="25"/>
       <c r="B155" s="27"/>
       <c r="C155" s="3"/>
@@ -10315,7 +10635,7 @@
       <c r="AH155" s="31"/>
       <c r="AI155" s="12"/>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156" s="25"/>
       <c r="B156" s="27"/>
       <c r="C156" s="3"/>
@@ -10358,7 +10678,7 @@
       <c r="AH156" s="31"/>
       <c r="AI156" s="12"/>
     </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157" s="25"/>
       <c r="B157" s="27"/>
       <c r="C157" s="3"/>
@@ -10401,7 +10721,7 @@
       <c r="AH157" s="31"/>
       <c r="AI157" s="12"/>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158" s="25"/>
       <c r="B158" s="27"/>
       <c r="C158" s="3"/>
@@ -10444,7 +10764,7 @@
       <c r="AH158" s="31"/>
       <c r="AI158" s="12"/>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159" s="18"/>
       <c r="B159" s="27"/>
       <c r="C159" s="8"/>
@@ -10487,7 +10807,7 @@
       <c r="AH159" s="31"/>
       <c r="AI159" s="12"/>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160" s="18"/>
       <c r="B160" s="27"/>
       <c r="C160" s="8"/>
@@ -10530,7 +10850,7 @@
       <c r="AH160" s="31"/>
       <c r="AI160" s="12"/>
     </row>
-    <row r="161" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161" s="18"/>
       <c r="B161" s="27"/>
       <c r="C161" s="8"/>
@@ -10573,7 +10893,7 @@
       <c r="AH161" s="31"/>
       <c r="AI161" s="12"/>
     </row>
-    <row r="162" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162" s="18"/>
       <c r="B162" s="27"/>
       <c r="C162" s="8"/>
@@ -10616,7 +10936,7 @@
       <c r="AH162" s="31"/>
       <c r="AI162" s="12"/>
     </row>
-    <row r="163" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163" s="18"/>
       <c r="B163" s="27"/>
       <c r="C163" s="8"/>
@@ -10659,7 +10979,7 @@
       <c r="AH163" s="31"/>
       <c r="AI163" s="12"/>
     </row>
-    <row r="164" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164" s="18"/>
       <c r="B164" s="27"/>
       <c r="C164" s="8"/>
@@ -10702,7 +11022,7 @@
       <c r="AH164" s="31"/>
       <c r="AI164" s="12"/>
     </row>
-    <row r="165" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165" s="18"/>
       <c r="B165" s="27"/>
       <c r="C165" s="3"/>
@@ -10745,7 +11065,7 @@
       <c r="AH165" s="31"/>
       <c r="AI165" s="12"/>
     </row>
-    <row r="166" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166" s="18"/>
       <c r="B166" s="27"/>
       <c r="C166" s="3"/>
@@ -10788,7 +11108,7 @@
       <c r="AH166" s="31"/>
       <c r="AI166" s="12"/>
     </row>
-    <row r="167" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167" s="18"/>
       <c r="B167" s="27"/>
       <c r="C167" s="3"/>
@@ -10831,7 +11151,7 @@
       <c r="AH167" s="31"/>
       <c r="AI167" s="12"/>
     </row>
-    <row r="168" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168" s="18"/>
       <c r="B168" s="27"/>
       <c r="C168" s="3"/>
@@ -10874,7 +11194,7 @@
       <c r="AH168" s="31"/>
       <c r="AI168" s="12"/>
     </row>
-    <row r="169" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169" s="18"/>
       <c r="B169" s="27"/>
       <c r="C169" s="3"/>
@@ -10917,7 +11237,7 @@
       <c r="AH169" s="31"/>
       <c r="AI169" s="12"/>
     </row>
-    <row r="170" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170" s="18"/>
       <c r="B170" s="27"/>
       <c r="C170" s="3"/>
@@ -10960,7 +11280,7 @@
       <c r="AH170" s="31"/>
       <c r="AI170" s="12"/>
     </row>
-    <row r="171" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171" s="18"/>
       <c r="B171" s="27"/>
       <c r="C171" s="8"/>
@@ -11003,7 +11323,7 @@
       <c r="AH171" s="32"/>
       <c r="AI171" s="6"/>
     </row>
-    <row r="172" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172" s="18"/>
       <c r="B172" s="27"/>
       <c r="C172" s="8"/>
@@ -11046,7 +11366,7 @@
       <c r="AH172" s="32"/>
       <c r="AI172" s="6"/>
     </row>
-    <row r="173" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A173" s="18"/>
       <c r="B173" s="27"/>
       <c r="C173" s="8"/>
@@ -11089,7 +11409,7 @@
       <c r="AH173" s="32"/>
       <c r="AI173" s="6"/>
     </row>
-    <row r="174" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174" s="18"/>
       <c r="B174" s="27"/>
       <c r="C174" s="8"/>
@@ -11132,7 +11452,7 @@
       <c r="AH174" s="32"/>
       <c r="AI174" s="6"/>
     </row>
-    <row r="175" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175" s="18"/>
       <c r="B175" s="27"/>
       <c r="C175" s="8"/>
@@ -11175,7 +11495,7 @@
       <c r="AH175" s="32"/>
       <c r="AI175" s="6"/>
     </row>
-    <row r="176" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A176" s="18"/>
       <c r="B176" s="27"/>
       <c r="C176" s="8"/>
@@ -11218,7 +11538,7 @@
       <c r="AH176" s="32"/>
       <c r="AI176" s="6"/>
     </row>
-    <row r="177" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A177" s="18"/>
       <c r="B177" s="27"/>
       <c r="C177" s="3"/>
@@ -11261,7 +11581,7 @@
       <c r="AH177" s="32"/>
       <c r="AI177" s="6"/>
     </row>
-    <row r="178" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A178" s="18"/>
       <c r="B178" s="27"/>
       <c r="C178" s="3"/>
@@ -11304,7 +11624,7 @@
       <c r="AH178" s="32"/>
       <c r="AI178" s="6"/>
     </row>
-    <row r="179" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A179" s="18"/>
       <c r="B179" s="27"/>
       <c r="C179" s="3"/>
@@ -11347,7 +11667,7 @@
       <c r="AH179" s="32"/>
       <c r="AI179" s="6"/>
     </row>
-    <row r="180" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A180" s="18"/>
       <c r="B180" s="27"/>
       <c r="C180" s="3"/>
@@ -11390,7 +11710,7 @@
       <c r="AH180" s="32"/>
       <c r="AI180" s="6"/>
     </row>
-    <row r="181" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A181" s="18"/>
       <c r="B181" s="27"/>
       <c r="C181" s="3"/>
@@ -11433,7 +11753,7 @@
       <c r="AH181" s="32"/>
       <c r="AI181" s="6"/>
     </row>
-    <row r="182" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A182" s="18"/>
       <c r="B182" s="27"/>
       <c r="C182" s="3"/>
@@ -11476,7 +11796,7 @@
       <c r="AH182" s="32"/>
       <c r="AI182" s="6"/>
     </row>
-    <row r="183" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A183" s="18"/>
       <c r="B183" s="27"/>
       <c r="C183" s="8"/>
@@ -11519,7 +11839,7 @@
       <c r="AH183" s="32"/>
       <c r="AI183" s="6"/>
     </row>
-    <row r="184" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A184" s="18"/>
       <c r="B184" s="27"/>
       <c r="C184" s="8"/>
@@ -11562,7 +11882,7 @@
       <c r="AH184" s="32"/>
       <c r="AI184" s="6"/>
     </row>
-    <row r="185" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A185" s="18"/>
       <c r="B185" s="27"/>
       <c r="C185" s="8"/>
@@ -11605,7 +11925,7 @@
       <c r="AH185" s="32"/>
       <c r="AI185" s="6"/>
     </row>
-    <row r="186" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A186" s="18"/>
       <c r="B186" s="27"/>
       <c r="C186" s="8"/>
@@ -11648,7 +11968,7 @@
       <c r="AH186" s="32"/>
       <c r="AI186" s="6"/>
     </row>
-    <row r="187" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A187" s="18"/>
       <c r="B187" s="27"/>
       <c r="C187" s="8"/>
@@ -11691,7 +12011,7 @@
       <c r="AH187" s="32"/>
       <c r="AI187" s="6"/>
     </row>
-    <row r="188" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A188" s="18"/>
       <c r="B188" s="27"/>
       <c r="C188" s="3"/>
@@ -11734,7 +12054,7 @@
       <c r="AH188" s="32"/>
       <c r="AI188" s="6"/>
     </row>
-    <row r="189" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A189" s="18"/>
       <c r="B189" s="27"/>
       <c r="C189" s="3"/>
@@ -11777,7 +12097,7 @@
       <c r="AH189" s="32"/>
       <c r="AI189" s="6"/>
     </row>
-    <row r="190" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A190" s="18"/>
       <c r="B190" s="27"/>
       <c r="C190" s="3"/>
@@ -11820,7 +12140,7 @@
       <c r="AH190" s="32"/>
       <c r="AI190" s="6"/>
     </row>
-    <row r="191" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A191" s="18"/>
       <c r="B191" s="27"/>
       <c r="C191" s="3"/>
@@ -11863,7 +12183,7 @@
       <c r="AH191" s="32"/>
       <c r="AI191" s="6"/>
     </row>
-    <row r="192" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A192" s="18"/>
       <c r="B192" s="27"/>
       <c r="C192" s="3"/>
@@ -11906,7 +12226,7 @@
       <c r="AH192" s="32"/>
       <c r="AI192" s="6"/>
     </row>
-    <row r="193" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A193" s="18"/>
       <c r="B193" s="27"/>
       <c r="C193" s="8"/>
@@ -11949,7 +12269,7 @@
       <c r="AH193" s="32"/>
       <c r="AI193" s="6"/>
     </row>
-    <row r="194" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A194" s="18"/>
       <c r="B194" s="27"/>
       <c r="C194" s="8"/>
@@ -11992,7 +12312,7 @@
       <c r="AH194" s="32"/>
       <c r="AI194" s="6"/>
     </row>
-    <row r="195" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A195" s="18"/>
       <c r="B195" s="27"/>
       <c r="C195" s="8"/>
@@ -12035,7 +12355,7 @@
       <c r="AH195" s="32"/>
       <c r="AI195" s="6"/>
     </row>
-    <row r="196" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A196" s="18"/>
       <c r="B196" s="27"/>
       <c r="C196" s="8"/>
@@ -12078,7 +12398,7 @@
       <c r="AH196" s="32"/>
       <c r="AI196" s="6"/>
     </row>
-    <row r="197" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A197" s="18"/>
       <c r="B197" s="27"/>
       <c r="C197" s="8"/>
@@ -12121,7 +12441,7 @@
       <c r="AH197" s="32"/>
       <c r="AI197" s="6"/>
     </row>
-    <row r="198" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A198" s="18"/>
       <c r="B198" s="27"/>
       <c r="C198" s="8"/>
@@ -12164,7 +12484,7 @@
       <c r="AH198" s="32"/>
       <c r="AI198" s="6"/>
     </row>
-    <row r="199" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A199" s="18"/>
       <c r="B199" s="27"/>
       <c r="C199" s="3"/>
@@ -12207,7 +12527,7 @@
       <c r="AH199" s="32"/>
       <c r="AI199" s="6"/>
     </row>
-    <row r="200" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A200" s="18"/>
       <c r="B200" s="27"/>
       <c r="C200" s="3"/>
@@ -12250,7 +12570,7 @@
       <c r="AH200" s="32"/>
       <c r="AI200" s="6"/>
     </row>
-    <row r="201" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A201" s="18"/>
       <c r="B201" s="27"/>
       <c r="C201" s="3"/>
@@ -12293,7 +12613,7 @@
       <c r="AH201" s="32"/>
       <c r="AI201" s="6"/>
     </row>
-    <row r="202" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A202" s="18"/>
       <c r="B202" s="27"/>
       <c r="C202" s="3"/>
@@ -12336,7 +12656,7 @@
       <c r="AH202" s="32"/>
       <c r="AI202" s="6"/>
     </row>
-    <row r="203" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A203" s="18"/>
       <c r="B203" s="27"/>
       <c r="C203" s="3"/>
@@ -12379,7 +12699,7 @@
       <c r="AH203" s="32"/>
       <c r="AI203" s="6"/>
     </row>
-    <row r="204" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A204" s="18"/>
       <c r="B204" s="27"/>
       <c r="C204" s="3"/>
@@ -12422,7 +12742,7 @@
       <c r="AH204" s="32"/>
       <c r="AI204" s="6"/>
     </row>
-    <row r="205" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A205" s="18"/>
       <c r="B205" s="27"/>
       <c r="C205" s="8"/>
@@ -12465,7 +12785,7 @@
       <c r="AH205" s="32"/>
       <c r="AI205" s="6"/>
     </row>
-    <row r="206" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A206" s="18"/>
       <c r="B206" s="27"/>
       <c r="C206" s="8"/>
@@ -12508,7 +12828,7 @@
       <c r="AH206" s="32"/>
       <c r="AI206" s="6"/>
     </row>
-    <row r="207" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="18"/>
       <c r="B207" s="27"/>
       <c r="C207" s="8"/>
@@ -12551,7 +12871,7 @@
       <c r="AH207" s="32"/>
       <c r="AI207" s="6"/>
     </row>
-    <row r="208" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A208" s="18"/>
       <c r="B208" s="27"/>
       <c r="C208" s="8"/>
@@ -12594,7 +12914,7 @@
       <c r="AH208" s="32"/>
       <c r="AI208" s="6"/>
     </row>
-    <row r="209" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A209" s="18"/>
       <c r="B209" s="27"/>
       <c r="C209" s="8"/>
@@ -12637,7 +12957,7 @@
       <c r="AH209" s="32"/>
       <c r="AI209" s="6"/>
     </row>
-    <row r="210" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A210" s="18"/>
       <c r="B210" s="27"/>
       <c r="C210" s="8"/>
@@ -12680,7 +13000,7 @@
       <c r="AH210" s="32"/>
       <c r="AI210" s="6"/>
     </row>
-    <row r="211" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A211" s="18"/>
       <c r="B211" s="27"/>
       <c r="C211" s="3"/>
@@ -12723,7 +13043,7 @@
       <c r="AH211" s="32"/>
       <c r="AI211" s="6"/>
     </row>
-    <row r="212" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A212" s="18"/>
       <c r="B212" s="27"/>
       <c r="C212" s="3"/>
@@ -12766,7 +13086,7 @@
       <c r="AH212" s="32"/>
       <c r="AI212" s="6"/>
     </row>
-    <row r="213" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A213" s="18"/>
       <c r="B213" s="27"/>
       <c r="C213" s="3"/>
@@ -12809,7 +13129,7 @@
       <c r="AH213" s="32"/>
       <c r="AI213" s="6"/>
     </row>
-    <row r="214" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A214" s="18"/>
       <c r="B214" s="27"/>
       <c r="C214" s="3"/>
@@ -12852,7 +13172,7 @@
       <c r="AH214" s="32"/>
       <c r="AI214" s="6"/>
     </row>
-    <row r="215" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A215" s="18"/>
       <c r="B215" s="27"/>
       <c r="C215" s="3"/>
@@ -12895,7 +13215,7 @@
       <c r="AH215" s="32"/>
       <c r="AI215" s="6"/>
     </row>
-    <row r="216" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A216" s="18"/>
       <c r="B216" s="27"/>
       <c r="C216" s="3"/>
@@ -12938,7 +13258,7 @@
       <c r="AH216" s="32"/>
       <c r="AI216" s="6"/>
     </row>
-    <row r="217" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A217" s="18"/>
       <c r="B217" s="27"/>
       <c r="C217" s="8"/>
@@ -12981,7 +13301,7 @@
       <c r="AH217" s="32"/>
       <c r="AI217" s="6"/>
     </row>
-    <row r="218" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A218" s="18"/>
       <c r="B218" s="27"/>
       <c r="C218" s="8"/>
@@ -13024,7 +13344,7 @@
       <c r="AH218" s="32"/>
       <c r="AI218" s="6"/>
     </row>
-    <row r="219" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A219" s="18"/>
       <c r="B219" s="27"/>
       <c r="C219" s="8"/>
@@ -13067,7 +13387,7 @@
       <c r="AH219" s="32"/>
       <c r="AI219" s="6"/>
     </row>
-    <row r="220" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A220" s="18"/>
       <c r="B220" s="27"/>
       <c r="C220" s="8"/>
@@ -13110,7 +13430,7 @@
       <c r="AH220" s="32"/>
       <c r="AI220" s="6"/>
     </row>
-    <row r="221" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A221" s="18"/>
       <c r="B221" s="27"/>
       <c r="C221" s="8"/>
@@ -13153,7 +13473,7 @@
       <c r="AH221" s="32"/>
       <c r="AI221" s="6"/>
     </row>
-    <row r="222" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A222" s="18"/>
       <c r="B222" s="27"/>
       <c r="C222" s="8"/>
@@ -13196,7 +13516,7 @@
       <c r="AH222" s="32"/>
       <c r="AI222" s="6"/>
     </row>
-    <row r="223" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A223" s="18"/>
       <c r="B223" s="27"/>
       <c r="C223" s="3"/>
@@ -13239,7 +13559,7 @@
       <c r="AH223" s="32"/>
       <c r="AI223" s="6"/>
     </row>
-    <row r="224" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A224" s="18"/>
       <c r="B224" s="27"/>
       <c r="C224" s="3"/>
@@ -13282,7 +13602,7 @@
       <c r="AH224" s="32"/>
       <c r="AI224" s="6"/>
     </row>
-    <row r="225" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A225" s="18"/>
       <c r="B225" s="27"/>
       <c r="C225" s="3"/>
@@ -13325,7 +13645,7 @@
       <c r="AH225" s="32"/>
       <c r="AI225" s="6"/>
     </row>
-    <row r="226" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A226" s="18"/>
       <c r="B226" s="27"/>
       <c r="C226" s="3"/>
@@ -13368,7 +13688,7 @@
       <c r="AH226" s="32"/>
       <c r="AI226" s="6"/>
     </row>
-    <row r="227" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A227" s="18"/>
       <c r="B227" s="27"/>
       <c r="C227" s="3"/>
@@ -13411,7 +13731,7 @@
       <c r="AH227" s="32"/>
       <c r="AI227" s="6"/>
     </row>
-    <row r="228" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A228" s="18"/>
       <c r="B228" s="27"/>
       <c r="C228" s="3"/>
@@ -13454,7 +13774,7 @@
       <c r="AH228" s="32"/>
       <c r="AI228" s="6"/>
     </row>
-    <row r="229" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A229" s="18"/>
       <c r="B229" s="27"/>
       <c r="C229" s="8"/>
@@ -13497,7 +13817,7 @@
       <c r="AH229" s="32"/>
       <c r="AI229" s="6"/>
     </row>
-    <row r="230" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A230" s="18"/>
       <c r="B230" s="27"/>
       <c r="C230" s="8"/>
@@ -13540,7 +13860,7 @@
       <c r="AH230" s="32"/>
       <c r="AI230" s="6"/>
     </row>
-    <row r="231" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A231" s="18"/>
       <c r="B231" s="27"/>
       <c r="C231" s="8"/>
@@ -13583,7 +13903,7 @@
       <c r="AH231" s="32"/>
       <c r="AI231" s="6"/>
     </row>
-    <row r="232" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A232" s="18"/>
       <c r="B232" s="27"/>
       <c r="C232" s="8"/>
@@ -13626,7 +13946,7 @@
       <c r="AH232" s="32"/>
       <c r="AI232" s="6"/>
     </row>
-    <row r="233" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A233" s="18"/>
       <c r="B233" s="27"/>
       <c r="C233" s="8"/>
@@ -13669,7 +13989,7 @@
       <c r="AH233" s="32"/>
       <c r="AI233" s="6"/>
     </row>
-    <row r="234" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A234" s="18"/>
       <c r="B234" s="27"/>
       <c r="C234" s="8"/>
@@ -13712,7 +14032,7 @@
       <c r="AH234" s="32"/>
       <c r="AI234" s="6"/>
     </row>
-    <row r="235" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A235" s="18"/>
       <c r="B235" s="27"/>
       <c r="C235" s="8"/>
@@ -13755,7 +14075,7 @@
       <c r="AH235" s="32"/>
       <c r="AI235" s="6"/>
     </row>
-    <row r="236" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A236" s="18"/>
       <c r="B236" s="27"/>
       <c r="C236" s="3"/>
@@ -13798,7 +14118,7 @@
       <c r="AH236" s="32"/>
       <c r="AI236" s="6"/>
     </row>
-    <row r="237" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A237" s="18"/>
       <c r="B237" s="27"/>
       <c r="C237" s="3"/>
@@ -13841,7 +14161,7 @@
       <c r="AH237" s="32"/>
       <c r="AI237" s="6"/>
     </row>
-    <row r="238" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A238" s="18"/>
       <c r="B238" s="27"/>
       <c r="C238" s="3"/>
@@ -13884,7 +14204,7 @@
       <c r="AH238" s="32"/>
       <c r="AI238" s="6"/>
     </row>
-    <row r="239" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A239" s="18"/>
       <c r="B239" s="27"/>
       <c r="C239" s="3"/>
@@ -13927,7 +14247,7 @@
       <c r="AH239" s="32"/>
       <c r="AI239" s="6"/>
     </row>
-    <row r="240" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A240" s="18"/>
       <c r="B240" s="27"/>
       <c r="C240" s="3"/>
@@ -13970,7 +14290,7 @@
       <c r="AH240" s="32"/>
       <c r="AI240" s="6"/>
     </row>
-    <row r="241" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A241" s="18"/>
       <c r="B241" s="27"/>
       <c r="C241" s="3"/>
@@ -14013,7 +14333,7 @@
       <c r="AH241" s="32"/>
       <c r="AI241" s="6"/>
     </row>
-    <row r="242" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A242" s="18"/>
       <c r="B242" s="28"/>
       <c r="C242" s="8"/>
@@ -14056,7 +14376,7 @@
       <c r="AH242" s="32"/>
       <c r="AI242" s="6"/>
     </row>
-    <row r="243" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A243" s="18"/>
       <c r="B243" s="28"/>
       <c r="C243" s="8"/>
@@ -14099,7 +14419,7 @@
       <c r="AH243" s="32"/>
       <c r="AI243" s="6"/>
     </row>
-    <row r="244" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A244" s="18"/>
       <c r="B244" s="28"/>
       <c r="C244" s="8"/>
@@ -14142,7 +14462,7 @@
       <c r="AH244" s="32"/>
       <c r="AI244" s="6"/>
     </row>
-    <row r="245" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A245" s="18"/>
       <c r="B245" s="28"/>
       <c r="C245" s="8"/>
@@ -14185,7 +14505,7 @@
       <c r="AH245" s="32"/>
       <c r="AI245" s="6"/>
     </row>
-    <row r="246" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A246" s="18"/>
       <c r="B246" s="28"/>
       <c r="C246" s="8"/>
@@ -14228,7 +14548,7 @@
       <c r="AH246" s="32"/>
       <c r="AI246" s="6"/>
     </row>
-    <row r="247" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A247" s="18"/>
       <c r="B247" s="28"/>
       <c r="C247" s="3"/>
@@ -14271,7 +14591,7 @@
       <c r="AH247" s="32"/>
       <c r="AI247" s="6"/>
     </row>
-    <row r="248" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A248" s="18"/>
       <c r="B248" s="28"/>
       <c r="C248" s="3"/>
@@ -14314,7 +14634,7 @@
       <c r="AH248" s="32"/>
       <c r="AI248" s="6"/>
     </row>
-    <row r="249" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A249" s="18"/>
       <c r="B249" s="28"/>
       <c r="C249" s="3"/>
@@ -14357,7 +14677,7 @@
       <c r="AH249" s="32"/>
       <c r="AI249" s="6"/>
     </row>
-    <row r="250" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A250" s="18"/>
       <c r="B250" s="28"/>
       <c r="C250" s="3"/>
@@ -14400,7 +14720,7 @@
       <c r="AH250" s="32"/>
       <c r="AI250" s="6"/>
     </row>
-    <row r="251" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A251" s="18"/>
       <c r="B251" s="28"/>
       <c r="C251" s="3"/>
@@ -14443,7 +14763,7 @@
       <c r="AH251" s="32"/>
       <c r="AI251" s="6"/>
     </row>
-    <row r="252" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A252" s="18"/>
       <c r="B252" s="28"/>
       <c r="C252" s="3"/>
@@ -14486,7 +14806,7 @@
       <c r="AH252" s="32"/>
       <c r="AI252" s="6"/>
     </row>
-    <row r="253" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A253" s="18"/>
       <c r="B253" s="28"/>
       <c r="C253" s="3"/>
@@ -14529,7 +14849,7 @@
       <c r="AH253" s="32"/>
       <c r="AI253" s="6"/>
     </row>
-    <row r="254" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A254" s="18"/>
       <c r="B254" s="28"/>
       <c r="C254" s="3"/>
@@ -14572,7 +14892,7 @@
       <c r="AH254" s="32"/>
       <c r="AI254" s="6"/>
     </row>
-    <row r="255" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A255" s="18"/>
       <c r="B255" s="28"/>
       <c r="C255" s="3"/>
@@ -14615,7 +14935,7 @@
       <c r="AH255" s="32"/>
       <c r="AI255" s="6"/>
     </row>
-    <row r="256" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A256" s="18"/>
       <c r="B256" s="28"/>
       <c r="C256" s="3"/>
@@ -14658,7 +14978,7 @@
       <c r="AH256" s="32"/>
       <c r="AI256" s="6"/>
     </row>
-    <row r="257" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A257" s="18"/>
       <c r="B257" s="28"/>
       <c r="C257" s="3"/>
@@ -14701,7 +15021,7 @@
       <c r="AH257" s="32"/>
       <c r="AI257" s="6"/>
     </row>
-    <row r="258" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A258" s="18"/>
       <c r="B258" s="28"/>
       <c r="C258" s="3"/>
@@ -14744,7 +15064,7 @@
       <c r="AH258" s="32"/>
       <c r="AI258" s="6"/>
     </row>
-    <row r="259" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A259" s="18"/>
       <c r="B259" s="28"/>
       <c r="C259" s="3"/>
@@ -14787,7 +15107,7 @@
       <c r="AH259" s="32"/>
       <c r="AI259" s="6"/>
     </row>
-    <row r="260" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A260" s="18"/>
       <c r="B260" s="28"/>
       <c r="C260" s="3"/>
@@ -14830,7 +15150,7 @@
       <c r="AH260" s="32"/>
       <c r="AI260" s="6"/>
     </row>
-    <row r="261" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A261" s="18"/>
       <c r="B261" s="28"/>
       <c r="C261" s="3"/>
@@ -14873,7 +15193,7 @@
       <c r="AH261" s="32"/>
       <c r="AI261" s="6"/>
     </row>
-    <row r="262" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A262" s="18"/>
       <c r="B262" s="28"/>
       <c r="C262" s="3"/>
@@ -14916,7 +15236,7 @@
       <c r="AH262" s="32"/>
       <c r="AI262" s="6"/>
     </row>
-    <row r="263" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A263" s="18"/>
       <c r="B263" s="28"/>
       <c r="C263" s="3"/>
@@ -14959,7 +15279,7 @@
       <c r="AH263" s="32"/>
       <c r="AI263" s="6"/>
     </row>
-    <row r="264" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A264" s="18"/>
       <c r="B264" s="28"/>
       <c r="C264" s="3"/>
@@ -15002,7 +15322,7 @@
       <c r="AH264" s="32"/>
       <c r="AI264" s="6"/>
     </row>
-    <row r="265" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A265" s="18"/>
       <c r="B265" s="28"/>
       <c r="C265" s="3"/>
@@ -15045,7 +15365,7 @@
       <c r="AH265" s="32"/>
       <c r="AI265" s="6"/>
     </row>
-    <row r="266" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A266" s="18"/>
       <c r="B266" s="28"/>
       <c r="C266" s="3"/>
@@ -15088,7 +15408,7 @@
       <c r="AH266" s="32"/>
       <c r="AI266" s="6"/>
     </row>
-    <row r="267" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A267" s="18"/>
       <c r="B267" s="28"/>
       <c r="C267" s="3"/>
@@ -15131,7 +15451,7 @@
       <c r="AH267" s="32"/>
       <c r="AI267" s="6"/>
     </row>
-    <row r="268" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A268" s="18"/>
       <c r="B268" s="28"/>
       <c r="C268" s="3"/>
@@ -15174,7 +15494,7 @@
       <c r="AH268" s="32"/>
       <c r="AI268" s="6"/>
     </row>
-    <row r="269" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A269" s="18"/>
       <c r="B269" s="28"/>
       <c r="C269" s="3"/>
@@ -15217,7 +15537,7 @@
       <c r="AH269" s="32"/>
       <c r="AI269" s="6"/>
     </row>
-    <row r="270" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A270" s="18"/>
       <c r="B270" s="28"/>
       <c r="C270" s="3"/>
@@ -15260,7 +15580,7 @@
       <c r="AH270" s="32"/>
       <c r="AI270" s="6"/>
     </row>
-    <row r="271" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A271" s="18"/>
       <c r="B271" s="28"/>
       <c r="C271" s="3"/>
@@ -15303,7 +15623,7 @@
       <c r="AH271" s="32"/>
       <c r="AI271" s="6"/>
     </row>
-    <row r="272" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A272" s="18"/>
       <c r="B272" s="28"/>
       <c r="C272" s="3"/>
@@ -15346,7 +15666,7 @@
       <c r="AH272" s="32"/>
       <c r="AI272" s="6"/>
     </row>
-    <row r="273" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A273" s="18"/>
       <c r="B273" s="28"/>
       <c r="C273" s="3"/>
@@ -15389,7 +15709,7 @@
       <c r="AH273" s="32"/>
       <c r="AI273" s="6"/>
     </row>
-    <row r="274" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A274" s="18"/>
       <c r="B274" s="28"/>
       <c r="C274" s="3"/>
@@ -15432,7 +15752,7 @@
       <c r="AH274" s="32"/>
       <c r="AI274" s="6"/>
     </row>
-    <row r="275" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A275" s="18"/>
       <c r="B275" s="28"/>
       <c r="C275" s="3"/>
@@ -15475,7 +15795,7 @@
       <c r="AH275" s="32"/>
       <c r="AI275" s="6"/>
     </row>
-    <row r="276" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A276" s="18"/>
       <c r="B276" s="28"/>
       <c r="C276" s="3"/>
@@ -15518,7 +15838,7 @@
       <c r="AH276" s="32"/>
       <c r="AI276" s="6"/>
     </row>
-    <row r="277" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A277" s="18"/>
       <c r="B277" s="28"/>
       <c r="C277" s="3"/>
@@ -15561,7 +15881,7 @@
       <c r="AH277" s="32"/>
       <c r="AI277" s="6"/>
     </row>
-    <row r="278" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A278" s="18"/>
       <c r="B278" s="28"/>
       <c r="C278" s="3"/>
@@ -15604,7 +15924,7 @@
       <c r="AH278" s="32"/>
       <c r="AI278" s="6"/>
     </row>
-    <row r="279" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A279" s="18"/>
       <c r="B279" s="28"/>
       <c r="C279" s="3"/>
@@ -15647,7 +15967,7 @@
       <c r="AH279" s="32"/>
       <c r="AI279" s="6"/>
     </row>
-    <row r="280" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A280" s="18"/>
       <c r="B280" s="28"/>
       <c r="C280" s="3"/>
@@ -15690,7 +16010,7 @@
       <c r="AH280" s="32"/>
       <c r="AI280" s="6"/>
     </row>
-    <row r="281" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A281" s="18"/>
       <c r="B281" s="28"/>
       <c r="C281" s="3"/>
@@ -15733,7 +16053,7 @@
       <c r="AH281" s="32"/>
       <c r="AI281" s="6"/>
     </row>
-    <row r="282" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A282" s="18"/>
       <c r="B282" s="28"/>
       <c r="C282" s="3"/>
@@ -15775,7 +16095,7 @@
       <c r="AH282" s="32"/>
       <c r="AI282" s="6"/>
     </row>
-    <row r="283" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A283" s="18"/>
       <c r="B283" s="28"/>
       <c r="C283" s="3"/>
@@ -15818,7 +16138,7 @@
       <c r="AH283" s="32"/>
       <c r="AI283" s="6"/>
     </row>
-    <row r="284" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A284" s="18"/>
       <c r="B284" s="28"/>
       <c r="C284" s="3"/>
@@ -15861,7 +16181,7 @@
       <c r="AH284" s="32"/>
       <c r="AI284" s="6"/>
     </row>
-    <row r="285" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A285" s="18"/>
       <c r="B285" s="28"/>
       <c r="C285" s="3"/>
@@ -15904,7 +16224,7 @@
       <c r="AH285" s="32"/>
       <c r="AI285" s="6"/>
     </row>
-    <row r="286" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A286" s="18"/>
       <c r="B286" s="28"/>
       <c r="C286" s="3"/>
@@ -15947,7 +16267,7 @@
       <c r="AH286" s="32"/>
       <c r="AI286" s="6"/>
     </row>
-    <row r="287" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A287" s="18"/>
       <c r="B287" s="28"/>
       <c r="C287" s="3"/>
@@ -15990,7 +16310,7 @@
       <c r="AH287" s="32"/>
       <c r="AI287" s="6"/>
     </row>
-    <row r="288" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A288" s="18"/>
       <c r="B288" s="28"/>
       <c r="C288" s="3"/>
@@ -16033,7 +16353,7 @@
       <c r="AH288" s="32"/>
       <c r="AI288" s="6"/>
     </row>
-    <row r="289" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A289" s="18"/>
       <c r="B289" s="28"/>
       <c r="C289" s="3"/>
@@ -16075,7 +16395,7 @@
       <c r="AH289" s="32"/>
       <c r="AI289" s="6"/>
     </row>
-    <row r="290" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A290" s="18"/>
       <c r="B290" s="28"/>
       <c r="C290" s="3"/>
@@ -16118,7 +16438,7 @@
       <c r="AH290" s="32"/>
       <c r="AI290" s="6"/>
     </row>
-    <row r="291" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A291" s="18"/>
       <c r="B291" s="28"/>
       <c r="C291" s="3"/>
@@ -16161,7 +16481,7 @@
       <c r="AH291" s="32"/>
       <c r="AI291" s="6"/>
     </row>
-    <row r="292" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A292" s="18"/>
       <c r="B292" s="28"/>
       <c r="C292" s="3"/>
@@ -16204,7 +16524,7 @@
       <c r="AH292" s="32"/>
       <c r="AI292" s="6"/>
     </row>
-    <row r="293" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A293" s="18"/>
       <c r="B293" s="28"/>
       <c r="C293" s="3"/>
@@ -16247,7 +16567,7 @@
       <c r="AH293" s="32"/>
       <c r="AI293" s="6"/>
     </row>
-    <row r="294" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A294" s="18"/>
       <c r="B294" s="28"/>
       <c r="C294" s="3"/>
@@ -16290,7 +16610,7 @@
       <c r="AH294" s="32"/>
       <c r="AI294" s="6"/>
     </row>
-    <row r="295" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A295" s="18"/>
       <c r="B295" s="28"/>
       <c r="C295" s="3"/>
@@ -16333,7 +16653,7 @@
       <c r="AH295" s="32"/>
       <c r="AI295" s="6"/>
     </row>
-    <row r="296" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A296" s="18"/>
       <c r="B296" s="28"/>
       <c r="C296" s="3"/>
@@ -16375,7 +16695,7 @@
       <c r="AH296" s="32"/>
       <c r="AI296" s="6"/>
     </row>
-    <row r="297" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A297" s="18"/>
       <c r="B297" s="28"/>
       <c r="C297" s="3"/>
@@ -16418,7 +16738,7 @@
       <c r="AH297" s="32"/>
       <c r="AI297" s="6"/>
     </row>
-    <row r="298" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A298" s="18"/>
       <c r="B298" s="28"/>
       <c r="C298" s="3"/>
@@ -16461,7 +16781,7 @@
       <c r="AH298" s="32"/>
       <c r="AI298" s="6"/>
     </row>
-    <row r="299" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A299" s="18"/>
       <c r="B299" s="28"/>
       <c r="C299" s="3"/>
@@ -16504,7 +16824,7 @@
       <c r="AH299" s="32"/>
       <c r="AI299" s="6"/>
     </row>
-    <row r="300" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A300" s="18"/>
       <c r="B300" s="28"/>
       <c r="C300" s="3"/>
@@ -16547,7 +16867,7 @@
       <c r="AH300" s="32"/>
       <c r="AI300" s="6"/>
     </row>
-    <row r="301" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A301" s="18"/>
       <c r="B301" s="28"/>
       <c r="C301" s="3"/>
@@ -16590,7 +16910,7 @@
       <c r="AH301" s="32"/>
       <c r="AI301" s="6"/>
     </row>
-    <row r="302" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A302" s="18"/>
       <c r="B302" s="28"/>
       <c r="C302" s="3"/>
@@ -16633,7 +16953,7 @@
       <c r="AH302" s="32"/>
       <c r="AI302" s="6"/>
     </row>
-    <row r="303" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A303" s="18"/>
       <c r="B303" s="28"/>
       <c r="C303" s="3"/>
@@ -16675,7 +16995,7 @@
       <c r="AH303" s="32"/>
       <c r="AI303" s="6"/>
     </row>
-    <row r="304" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A304" s="18"/>
       <c r="B304" s="28"/>
       <c r="C304" s="3"/>
@@ -16718,7 +17038,7 @@
       <c r="AH304" s="32"/>
       <c r="AI304" s="6"/>
     </row>
-    <row r="305" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A305" s="18"/>
       <c r="B305" s="28"/>
       <c r="C305" s="3"/>
@@ -16761,7 +17081,7 @@
       <c r="AH305" s="32"/>
       <c r="AI305" s="6"/>
     </row>
-    <row r="306" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A306" s="18"/>
       <c r="B306" s="28"/>
       <c r="C306" s="3"/>
@@ -16804,7 +17124,7 @@
       <c r="AH306" s="32"/>
       <c r="AI306" s="6"/>
     </row>
-    <row r="307" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A307" s="18"/>
       <c r="B307" s="28"/>
       <c r="C307" s="3"/>
@@ -16847,7 +17167,7 @@
       <c r="AH307" s="32"/>
       <c r="AI307" s="6"/>
     </row>
-    <row r="308" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A308" s="18"/>
       <c r="B308" s="28"/>
       <c r="C308" s="3"/>
@@ -16890,7 +17210,7 @@
       <c r="AH308" s="32"/>
       <c r="AI308" s="6"/>
     </row>
-    <row r="309" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A309" s="18"/>
       <c r="B309" s="28"/>
       <c r="C309" s="3"/>
@@ -16933,7 +17253,7 @@
       <c r="AH309" s="32"/>
       <c r="AI309" s="6"/>
     </row>
-    <row r="310" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A310" s="18"/>
       <c r="B310" s="28"/>
       <c r="C310" s="3"/>
@@ -16975,7 +17295,7 @@
       <c r="AH310" s="32"/>
       <c r="AI310" s="6"/>
     </row>
-    <row r="311" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A311" s="18"/>
       <c r="B311" s="28"/>
       <c r="C311" s="3"/>
@@ -17018,7 +17338,7 @@
       <c r="AH311" s="32"/>
       <c r="AI311" s="6"/>
     </row>
-    <row r="312" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A312" s="18"/>
       <c r="B312" s="28"/>
       <c r="C312" s="3"/>
@@ -17061,7 +17381,7 @@
       <c r="AH312" s="32"/>
       <c r="AI312" s="6"/>
     </row>
-    <row r="313" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A313" s="18"/>
       <c r="B313" s="28"/>
       <c r="C313" s="3"/>
@@ -17104,7 +17424,7 @@
       <c r="AH313" s="32"/>
       <c r="AI313" s="6"/>
     </row>
-    <row r="314" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A314" s="18"/>
       <c r="B314" s="28"/>
       <c r="C314" s="3"/>
@@ -17147,7 +17467,7 @@
       <c r="AH314" s="32"/>
       <c r="AI314" s="6"/>
     </row>
-    <row r="315" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A315" s="18"/>
       <c r="B315" s="28"/>
       <c r="C315" s="3"/>
@@ -17190,7 +17510,7 @@
       <c r="AH315" s="32"/>
       <c r="AI315" s="6"/>
     </row>
-    <row r="316" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A316" s="18"/>
       <c r="B316" s="28"/>
       <c r="C316" s="3"/>
@@ -17233,7 +17553,7 @@
       <c r="AH316" s="32"/>
       <c r="AI316" s="6"/>
     </row>
-    <row r="317" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A317" s="18"/>
       <c r="B317" s="28"/>
       <c r="C317" s="3"/>
@@ -17275,7 +17595,7 @@
       <c r="AH317" s="32"/>
       <c r="AI317" s="6"/>
     </row>
-    <row r="318" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A318" s="18"/>
       <c r="B318" s="28"/>
       <c r="C318" s="3"/>
@@ -17318,7 +17638,7 @@
       <c r="AH318" s="32"/>
       <c r="AI318" s="6"/>
     </row>
-    <row r="319" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A319" s="18"/>
       <c r="B319" s="28"/>
       <c r="C319" s="3"/>
@@ -17361,7 +17681,7 @@
       <c r="AH319" s="32"/>
       <c r="AI319" s="6"/>
     </row>
-    <row r="320" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A320" s="18"/>
       <c r="B320" s="28"/>
       <c r="C320" s="3"/>
@@ -17404,7 +17724,7 @@
       <c r="AH320" s="32"/>
       <c r="AI320" s="6"/>
     </row>
-    <row r="321" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A321" s="18"/>
       <c r="B321" s="28"/>
       <c r="C321" s="3"/>
@@ -17447,7 +17767,7 @@
       <c r="AH321" s="32"/>
       <c r="AI321" s="6"/>
     </row>
-    <row r="322" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A322" s="18"/>
       <c r="B322" s="28"/>
       <c r="C322" s="3"/>
@@ -17490,7 +17810,7 @@
       <c r="AH322" s="32"/>
       <c r="AI322" s="6"/>
     </row>
-    <row r="323" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A323" s="18"/>
       <c r="B323" s="28"/>
       <c r="C323" s="3"/>
@@ -17533,7 +17853,7 @@
       <c r="AH323" s="32"/>
       <c r="AI323" s="6"/>
     </row>
-    <row r="324" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A324" s="18"/>
       <c r="B324" s="28"/>
       <c r="C324" s="3"/>
@@ -17575,7 +17895,7 @@
       <c r="AH324" s="32"/>
       <c r="AI324" s="6"/>
     </row>
-    <row r="325" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A325" s="18"/>
       <c r="B325" s="28"/>
       <c r="C325" s="3"/>
@@ -17618,7 +17938,7 @@
       <c r="AH325" s="32"/>
       <c r="AI325" s="6"/>
     </row>
-    <row r="326" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A326" s="18"/>
       <c r="B326" s="28"/>
       <c r="C326" s="3"/>
@@ -17661,7 +17981,7 @@
       <c r="AH326" s="32"/>
       <c r="AI326" s="6"/>
     </row>
-    <row r="327" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A327" s="18"/>
       <c r="B327" s="28"/>
       <c r="C327" s="3"/>
@@ -17704,7 +18024,7 @@
       <c r="AH327" s="32"/>
       <c r="AI327" s="6"/>
     </row>
-    <row r="328" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A328" s="18"/>
       <c r="B328" s="28"/>
       <c r="C328" s="3"/>
@@ -17747,7 +18067,7 @@
       <c r="AH328" s="32"/>
       <c r="AI328" s="6"/>
     </row>
-    <row r="329" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A329" s="18"/>
       <c r="B329" s="28"/>
       <c r="C329" s="3"/>
@@ -17790,7 +18110,7 @@
       <c r="AH329" s="32"/>
       <c r="AI329" s="6"/>
     </row>
-    <row r="330" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A330" s="18"/>
       <c r="B330" s="28"/>
       <c r="C330" s="3"/>
@@ -17833,7 +18153,7 @@
       <c r="AH330" s="32"/>
       <c r="AI330" s="6"/>
     </row>
-    <row r="331" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A331" s="18"/>
       <c r="B331" s="28"/>
       <c r="C331" s="3"/>
@@ -17875,7 +18195,7 @@
       <c r="AH331" s="32"/>
       <c r="AI331" s="6"/>
     </row>
-    <row r="332" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A332" s="18"/>
       <c r="B332" s="28"/>
       <c r="C332" s="3"/>
@@ -17918,7 +18238,7 @@
       <c r="AH332" s="32"/>
       <c r="AI332" s="6"/>
     </row>
-    <row r="333" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A333" s="18"/>
       <c r="B333" s="28"/>
       <c r="C333" s="3"/>
@@ -17961,7 +18281,7 @@
       <c r="AH333" s="32"/>
       <c r="AI333" s="6"/>
     </row>
-    <row r="334" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A334" s="18"/>
       <c r="B334" s="28"/>
       <c r="C334" s="3"/>
@@ -18004,7 +18324,7 @@
       <c r="AH334" s="32"/>
       <c r="AI334" s="6"/>
     </row>
-    <row r="335" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A335" s="18"/>
       <c r="B335" s="28"/>
       <c r="C335" s="3"/>
@@ -18047,7 +18367,7 @@
       <c r="AH335" s="32"/>
       <c r="AI335" s="6"/>
     </row>
-    <row r="336" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A336" s="39"/>
       <c r="B336" s="40"/>
       <c r="C336" s="41"/>
@@ -18090,7 +18410,7 @@
       <c r="AH336" s="32"/>
       <c r="AI336" s="6"/>
     </row>
-    <row r="337" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A337" s="39"/>
       <c r="B337" s="40"/>
       <c r="C337" s="41"/>
@@ -18133,7 +18453,7 @@
       <c r="AH337" s="32"/>
       <c r="AI337" s="6"/>
     </row>
-    <row r="338" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A338" s="39"/>
       <c r="B338" s="40"/>
       <c r="C338" s="41"/>
@@ -18175,7 +18495,7 @@
       <c r="AH338" s="32"/>
       <c r="AI338" s="6"/>
     </row>
-    <row r="339" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A339" s="39"/>
       <c r="B339" s="40"/>
       <c r="C339" s="41"/>
@@ -18218,7 +18538,7 @@
       <c r="AH339" s="32"/>
       <c r="AI339" s="6"/>
     </row>
-    <row r="340" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A340" s="39"/>
       <c r="B340" s="40"/>
       <c r="C340" s="41"/>
@@ -18261,7 +18581,7 @@
       <c r="AH340" s="32"/>
       <c r="AI340" s="6"/>
     </row>
-    <row r="341" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A341" s="39"/>
       <c r="B341" s="40"/>
       <c r="C341" s="41"/>
@@ -18304,7 +18624,7 @@
       <c r="AH341" s="32"/>
       <c r="AI341" s="6"/>
     </row>
-    <row r="342" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A342" s="39"/>
       <c r="B342" s="40"/>
       <c r="C342" s="41"/>
@@ -18347,7 +18667,7 @@
       <c r="AH342" s="32"/>
       <c r="AI342" s="6"/>
     </row>
-    <row r="343" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A343" s="39"/>
       <c r="B343" s="40"/>
       <c r="C343" s="41"/>
@@ -18390,7 +18710,7 @@
       <c r="AH343" s="32"/>
       <c r="AI343" s="6"/>
     </row>
-    <row r="344" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A344" s="39"/>
       <c r="B344" s="40"/>
       <c r="C344" s="41"/>
@@ -18432,7 +18752,7 @@
       <c r="AH344" s="32"/>
       <c r="AI344" s="6"/>
     </row>
-    <row r="345" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A345" s="39"/>
       <c r="B345" s="40"/>
       <c r="C345" s="41"/>
@@ -18475,7 +18795,7 @@
       <c r="AH345" s="32"/>
       <c r="AI345" s="6"/>
     </row>
-    <row r="346" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A346" s="39"/>
       <c r="B346" s="40"/>
       <c r="C346" s="41"/>
@@ -18518,7 +18838,7 @@
       <c r="AH346" s="32"/>
       <c r="AI346" s="6"/>
     </row>
-    <row r="347" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A347" s="39"/>
       <c r="B347" s="40"/>
       <c r="C347" s="41"/>
@@ -18561,7 +18881,7 @@
       <c r="AH347" s="32"/>
       <c r="AI347" s="6"/>
     </row>
-    <row r="348" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A348" s="39"/>
       <c r="B348" s="40"/>
       <c r="C348" s="41"/>
@@ -18604,7 +18924,7 @@
       <c r="AH348" s="32"/>
       <c r="AI348" s="6"/>
     </row>
-    <row r="349" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A349" s="18"/>
       <c r="B349" s="28"/>
       <c r="C349" s="3"/>
@@ -18647,7 +18967,7 @@
       <c r="AH349" s="32"/>
       <c r="AI349" s="6"/>
     </row>
-    <row r="350" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A350" s="18"/>
       <c r="B350" s="28"/>
       <c r="C350" s="3"/>
@@ -18690,7 +19010,7 @@
       <c r="AH350" s="32"/>
       <c r="AI350" s="6"/>
     </row>
-    <row r="351" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A351" s="18"/>
       <c r="B351" s="28"/>
       <c r="C351" s="3"/>
@@ -18732,7 +19052,7 @@
       <c r="AH351" s="32"/>
       <c r="AI351" s="6"/>
     </row>
-    <row r="352" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A352" s="18"/>
       <c r="B352" s="28"/>
       <c r="C352" s="3"/>
@@ -18775,7 +19095,7 @@
       <c r="AH352" s="32"/>
       <c r="AI352" s="6"/>
     </row>
-    <row r="353" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A353" s="18"/>
       <c r="B353" s="28"/>
       <c r="C353" s="3"/>
@@ -18818,7 +19138,7 @@
       <c r="AH353" s="32"/>
       <c r="AI353" s="6"/>
     </row>
-    <row r="354" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A354" s="18"/>
       <c r="B354" s="28"/>
       <c r="C354" s="3"/>
@@ -18861,7 +19181,7 @@
       <c r="AH354" s="32"/>
       <c r="AI354" s="6"/>
     </row>
-    <row r="355" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A355" s="18"/>
       <c r="B355" s="28"/>
       <c r="C355" s="3"/>
@@ -18904,7 +19224,7 @@
       <c r="AH355" s="32"/>
       <c r="AI355" s="6"/>
     </row>
-    <row r="356" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A356" s="18"/>
       <c r="B356" s="28"/>
       <c r="C356" s="3"/>
@@ -18947,7 +19267,7 @@
       <c r="AH356" s="32"/>
       <c r="AI356" s="6"/>
     </row>
-    <row r="357" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A357" s="18"/>
       <c r="B357" s="28"/>
       <c r="C357" s="3"/>
@@ -18990,7 +19310,7 @@
       <c r="AH357" s="32"/>
       <c r="AI357" s="6"/>
     </row>
-    <row r="358" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A358" s="18"/>
       <c r="B358" s="28"/>
       <c r="C358" s="3"/>
@@ -19033,7 +19353,7 @@
       <c r="AH358" s="32"/>
       <c r="AI358" s="6"/>
     </row>
-    <row r="359" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A359" s="18"/>
       <c r="B359" s="28"/>
       <c r="C359" s="3"/>
@@ -19075,7 +19395,7 @@
       <c r="AH359" s="32"/>
       <c r="AI359" s="6"/>
     </row>
-    <row r="360" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A360" s="18"/>
       <c r="B360" s="28"/>
       <c r="C360" s="3"/>
@@ -19118,7 +19438,7 @@
       <c r="AH360" s="32"/>
       <c r="AI360" s="6"/>
     </row>
-    <row r="361" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A361" s="18"/>
       <c r="B361" s="28"/>
       <c r="C361" s="3"/>
@@ -19161,7 +19481,7 @@
       <c r="AH361" s="32"/>
       <c r="AI361" s="6"/>
     </row>
-    <row r="362" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A362" s="18"/>
       <c r="B362" s="28"/>
       <c r="C362" s="3"/>
@@ -19204,7 +19524,7 @@
       <c r="AH362" s="32"/>
       <c r="AI362" s="6"/>
     </row>
-    <row r="363" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A363" s="18"/>
       <c r="B363" s="28"/>
       <c r="C363" s="3"/>
@@ -19247,7 +19567,7 @@
       <c r="AH363" s="32"/>
       <c r="AI363" s="6"/>
     </row>
-    <row r="364" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A364" s="18"/>
       <c r="B364" s="28"/>
       <c r="C364" s="3"/>
@@ -19290,7 +19610,7 @@
       <c r="AH364" s="32"/>
       <c r="AI364" s="6"/>
     </row>
-    <row r="365" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A365" s="18"/>
       <c r="B365" s="28"/>
       <c r="C365" s="3"/>
@@ -19332,7 +19652,7 @@
       <c r="AH365" s="32"/>
       <c r="AI365" s="6"/>
     </row>
-    <row r="366" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A366" s="18"/>
       <c r="B366" s="28"/>
       <c r="C366" s="3"/>
@@ -19375,7 +19695,7 @@
       <c r="AH366" s="32"/>
       <c r="AI366" s="6"/>
     </row>
-    <row r="367" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A367" s="18"/>
       <c r="B367" s="28"/>
       <c r="C367" s="3"/>
@@ -19418,7 +19738,7 @@
       <c r="AH367" s="32"/>
       <c r="AI367" s="6"/>
     </row>
-    <row r="368" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A368" s="18"/>
       <c r="B368" s="28"/>
       <c r="C368" s="3"/>
@@ -19461,7 +19781,7 @@
       <c r="AH368" s="32"/>
       <c r="AI368" s="6"/>
     </row>
-    <row r="369" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A369" s="18"/>
       <c r="B369" s="28"/>
       <c r="C369" s="3"/>
@@ -19504,7 +19824,7 @@
       <c r="AH369" s="32"/>
       <c r="AI369" s="6"/>
     </row>
-    <row r="370" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="19"/>
       <c r="B370" s="29"/>
       <c r="C370" s="20"/>
@@ -19547,7 +19867,7 @@
       <c r="AH370" s="33"/>
       <c r="AI370" s="24"/>
     </row>
-    <row r="371" spans="1:35" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="371" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
